--- a/Result/profitability/4907.xlsx
+++ b/Result/profitability/4907.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8787499999999999</v>
+        <v>0.9337500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>20.775</v>
+        <v>21.97125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-2.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1749999999999999</v>
+        <v>0.605</v>
       </c>
       <c r="N3" t="n">
-        <v>14.38</v>
+        <v>18.74</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07624999999999993</v>
+        <v>0.50625</v>
       </c>
       <c r="N4" t="n">
-        <v>10.67375</v>
+        <v>13.505</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1012499999999999</v>
+        <v>0.53875</v>
       </c>
       <c r="N5" t="n">
-        <v>8.081249999999999</v>
+        <v>10.405</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,16 +1137,16 @@
         <v>-1.18</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07625000000000005</v>
+        <v>0.2825</v>
       </c>
       <c r="N6" t="n">
-        <v>5.751250000000001</v>
+        <v>8.635</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4787500000000001</v>
+        <v>0.01124999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2775</v>
+        <v>6.37375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.43875</v>
+        <v>-0.31625</v>
       </c>
       <c r="N8" t="n">
-        <v>6.2375</v>
+        <v>5.95</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4907</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1448</v>
+      </c>
+      <c r="D75" t="n">
+        <v>824</v>
+      </c>
+      <c r="E75" t="n">
+        <v>624</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>556</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>38.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>557</v>
+      </c>
+      <c r="K75" t="n">
+        <v>442</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.41625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.72625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9800000000000004</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3550724637681162</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.299999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05062733876293191</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>14.58333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.7575387123064385</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
